--- a/output/pdf_financials_xlsx/MTY.xlsx
+++ b/output/pdf_financials_xlsx/MTY.xlsx
@@ -6288,31 +6288,31 @@
         <v>0.481</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>-13.069</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>1.112</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.509</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>-11.185</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>-18.315</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>17.773</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>30.269</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>58.315</v>
       </c>
     </row>
     <row r="93">
@@ -12694,7 +12694,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MTY.xlsx
+++ b/output/pdf_financials_xlsx/MTY.xlsx
@@ -1113,58 +1113,58 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.71489</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.212945</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.195897</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.357</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.282</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.487</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.118</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.144</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.287</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.439</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.649</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.856</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.408</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.198</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.253</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>1.048</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.627</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0</v>
+        <v>0.343</v>
       </c>
     </row>
     <row r="13">
@@ -2106,58 +2106,58 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>9.911505999999999</v>
+        <v>9.196616000000001</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>12.261503</v>
+        <v>12.048558</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>15.446794</v>
+        <v>15.250897</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>22.821</v>
+        <v>22.464</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>30.504</v>
+        <v>30.222</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>34.61</v>
+        <v>34.123</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>34.308</v>
+        <v>34.19</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>35.903</v>
+        <v>35.759</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>68.68600000000001</v>
+        <v>68.399</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>62.664</v>
+        <v>62.225</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>80.008</v>
+        <v>79.35899999999999</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>97.997</v>
+        <v>97.14100000000001</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-51.949</v>
+        <v>-52.357</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>112.072</v>
+        <v>111.874</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>96.17</v>
+        <v>95.917</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>109.985</v>
+        <v>108.937</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>15.805</v>
+        <v>15.178</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>138.242</v>
+        <v>137.899</v>
       </c>
     </row>
     <row r="28">
@@ -2228,58 +2228,58 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>9.911505999999999</v>
+        <v>9.196616000000001</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>12.261503</v>
+        <v>12.048558</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>15.446794</v>
+        <v>15.250897</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>22.821</v>
+        <v>22.464</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>30.504</v>
+        <v>30.222</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>34.61</v>
+        <v>34.123</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>34.308</v>
+        <v>34.19</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>35.903</v>
+        <v>35.759</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>68.68600000000001</v>
+        <v>68.399</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>62.664</v>
+        <v>62.225</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>80.008</v>
+        <v>79.35899999999999</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>97.997</v>
+        <v>97.14100000000001</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-51.949</v>
+        <v>-52.357</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>112.072</v>
+        <v>111.874</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>96.17</v>
+        <v>95.917</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>109.985</v>
+        <v>108.937</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>15.805</v>
+        <v>15.178</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>138.242</v>
+        <v>137.899</v>
       </c>
     </row>
     <row r="30">
@@ -2289,19 +2289,19 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>28.9479661536081</v>
+        <v>26.86002800136838</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>23.79128689031046</v>
+        <v>23.37810462490163</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>23.09405877941689</v>
+        <v>22.80117879197669</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>29.12402052119758</v>
+        <v>28.66841930626101</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>31.70234878403658</v>
+        <v>31.4092704219497</v>
       </c>
       <c r="G30" s="1" t="inlineStr">
         <is>
@@ -2309,16 +2309,16 @@
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>29.78719709664256</v>
+        <v>29.68474608645824</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>24.72607315275855</v>
+        <v>24.62690164803757</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>35.90955430662658</v>
+        <v>35.75950856097242</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>22.69752212197057</v>
+        <v>22.53851196922665</v>
       </c>
       <c r="L30" s="1" t="inlineStr">
         <is>
@@ -2515,10 +2515,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.819349</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.245844</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>5.637</v>
@@ -2533,40 +2533,40 @@
         <v>6.136</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>6.701</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>33.417</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>36.26</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>56.453</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>32.304</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>50.737</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>44.302</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>61.231</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>59.479</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>58.895</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>50.409</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>51.989</v>
       </c>
     </row>
     <row r="35">
@@ -2637,10 +2637,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.819349</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.245844</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>5.637</v>
@@ -2655,40 +2655,40 @@
         <v>6.136</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>6.701</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>33.417</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>36.26</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>56.453</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>32.304</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>50.737</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>44.302</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>61.231</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>59.479</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>58.895</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>50.409</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>51.989</v>
       </c>
     </row>
     <row r="37">
@@ -3369,10 +3369,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>15.777073</v>
+        <v>14.957724</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>15.548584</v>
+        <v>14.30274</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>20.871</v>
@@ -3387,40 +3387,40 @@
         <v>1.807</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>7.746</v>
+        <v>1.045</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>34.037</v>
+        <v>0.62</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>44.16</v>
+        <v>7.9</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>64.925</v>
+        <v>8.472</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>40.911</v>
+        <v>8.606999999999999</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>73.672</v>
+        <v>22.935</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>141.334</v>
+        <v>97.032</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>161.064</v>
+        <v>99.833</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>163.603</v>
+        <v>104.124</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>171.941</v>
+        <v>113.046</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>157.912</v>
+        <v>107.503</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>154.151</v>
+        <v>102.162</v>
       </c>
     </row>
     <row r="49">
@@ -8289,22 +8289,22 @@
         <v>-73.852</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>-109.137</v>
+        <v>-122.163</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>-102.238</v>
+        <v>-117.592</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>-80.214</v>
+        <v>-99.17400000000001</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>-110.388</v>
+        <v>-154.027</v>
       </c>
       <c r="R124" s="3" t="n">
-        <v>-102.306</v>
+        <v>-146.121</v>
       </c>
       <c r="S124" s="3" t="n">
-        <v>-69.87</v>
+        <v>-115.534</v>
       </c>
     </row>
     <row r="125">
@@ -8350,22 +8350,22 @@
         <v>-73.852</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>-109.137</v>
+        <v>-122.163</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>-102.238</v>
+        <v>-117.592</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>-80.214</v>
+        <v>-99.17400000000001</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>-110.388</v>
+        <v>-154.027</v>
       </c>
       <c r="R125" s="3" t="n">
-        <v>-102.306</v>
+        <v>-146.121</v>
       </c>
       <c r="S125" s="3" t="n">
-        <v>-69.87</v>
+        <v>-115.534</v>
       </c>
     </row>
     <row r="126">
@@ -9174,7 +9174,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -34718,7 +34718,11 @@
           <t>Net lease payments 10</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr"/>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E251" t="inlineStr">
         <is>
           <t>-</t>
@@ -37696,7 +37700,11 @@
           <t>Net lease payments 11</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr"/>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E280" t="inlineStr">
         <is>
           <t>-</t>
@@ -43020,7 +43028,11 @@
           <t>Net lease payments 12</t>
         </is>
       </c>
-      <c r="D331" t="inlineStr"/>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E331" t="inlineStr">
         <is>
           <t>-</t>
@@ -68352,7 +68364,7 @@
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E573" t="inlineStr">
@@ -72398,7 +72410,7 @@
       </c>
       <c r="D612" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E612" t="inlineStr">
@@ -78340,7 +78352,7 @@
       </c>
       <c r="D669" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E669" t="inlineStr">
@@ -89520,7 +89532,7 @@
       </c>
       <c r="D776" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E776" s="5" t="n">

--- a/output/pdf_financials_xlsx/MTY.xlsx
+++ b/output/pdf_financials_xlsx/MTY.xlsx
@@ -2167,58 +2167,58 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0</v>
+        <v>1.697228</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>2.825282</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>3.024716</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>4.412</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>4.995</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>5.331</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>7.076</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>8.279</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>12.844</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>22.902</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0</v>
+        <v>27.504</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0</v>
+        <v>33.208</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0</v>
+        <v>30.876</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0</v>
+        <v>28.442</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0</v>
+        <v>29.473</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>0</v>
+        <v>34.559</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>0</v>
+        <v>31.87</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>0</v>
+        <v>32.684</v>
       </c>
     </row>
     <row r="29">
@@ -2228,58 +2228,58 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>9.196616000000001</v>
+        <v>10.893844</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>12.048558</v>
+        <v>14.87384</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>15.250897</v>
+        <v>18.275613</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>22.464</v>
+        <v>26.876</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>30.222</v>
+        <v>35.217</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>34.123</v>
+        <v>39.454</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>34.19</v>
+        <v>41.266</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>35.759</v>
+        <v>44.038</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>68.399</v>
+        <v>81.24299999999999</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>62.225</v>
+        <v>85.127</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>79.35899999999999</v>
+        <v>106.863</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>97.14100000000001</v>
+        <v>130.349</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-52.357</v>
+        <v>-21.481</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>111.874</v>
+        <v>140.316</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>95.917</v>
+        <v>125.39</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>108.937</v>
+        <v>143.496</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>15.178</v>
+        <v>47.048</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>137.899</v>
+        <v>170.583</v>
       </c>
     </row>
     <row r="30">
@@ -2289,19 +2289,19 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>26.86002800136838</v>
+        <v>31.81702431443684</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>23.37810462490163</v>
+        <v>28.86006671454351</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>22.80117879197669</v>
+        <v>27.32334495118375</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>28.66841930626101</v>
+        <v>34.29898670205978</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>31.4092704219497</v>
+        <v>36.60049885678653</v>
       </c>
       <c r="G30" s="1" t="inlineStr">
         <is>
@@ -2309,16 +2309,16 @@
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>29.68474608645824</v>
+        <v>35.82833378191827</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>24.62690164803757</v>
+        <v>30.32857447848873</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>35.75950856097242</v>
+        <v>42.47444778460332</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>22.53851196922665</v>
+        <v>30.83384344563048</v>
       </c>
       <c r="L30" s="1" t="inlineStr">
         <is>
@@ -6787,58 +6787,58 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>1.697228</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>2.825282</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>3.024716</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>4.412</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>4.995</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>5.331</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>7.076</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>8.279</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>12.844</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>22.902</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>27.504</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>33.208</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>30.876</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>28.442</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>29.473</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>34.559</v>
       </c>
       <c r="R100" s="3" t="n">
-        <v>0</v>
+        <v>31.87</v>
       </c>
       <c r="S100" s="3" t="n">
-        <v>0</v>
+        <v>32.684</v>
       </c>
     </row>
     <row r="101">
@@ -7528,22 +7528,22 @@
         <v>0</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>1.655</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>1.108</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>1.041</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>2.034</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>4.853</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>3.971</v>
       </c>
       <c r="K112" s="3" t="n">
         <v>0</v>
@@ -7555,22 +7555,22 @@
         <v>0</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>0</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="O112" s="3" t="n">
-        <v>0</v>
+        <v>6.465</v>
       </c>
       <c r="P112" s="3" t="n">
-        <v>0</v>
+        <v>1.131</v>
       </c>
       <c r="Q112" s="3" t="n">
-        <v>0</v>
+        <v>1.689</v>
       </c>
       <c r="R112" s="3" t="n">
-        <v>0</v>
+        <v>4.302</v>
       </c>
       <c r="S112" s="3" t="n">
-        <v>0</v>
+        <v>7.675</v>
       </c>
     </row>
     <row r="113">
@@ -32278,7 +32278,11 @@
           <t>Amortization – intangible assets 12</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr"/>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E227" t="inlineStr">
         <is>
           <t>-</t>
@@ -34124,7 +34128,11 @@
           <t>Additions to intangible assets 12</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr"/>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E245" t="inlineStr">
         <is>
           <t>-</t>
@@ -34220,7 +34228,11 @@
           <t>Proceeds on disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr"/>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E246" t="inlineStr">
         <is>
           <t>-</t>
@@ -36046,7 +36058,11 @@
           <t>Amortization – intangible assets 13</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr"/>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E264" t="inlineStr">
         <is>
           <t>-</t>
@@ -37396,7 +37412,11 @@
           <t>Additions to intangible assets 13</t>
         </is>
       </c>
-      <c r="D277" t="inlineStr"/>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E277" t="inlineStr">
         <is>
           <t>-</t>
@@ -40522,7 +40542,11 @@
           <t>Amortization – intangible assets 14</t>
         </is>
       </c>
-      <c r="D307" t="inlineStr"/>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E307" t="inlineStr">
         <is>
           <t>-</t>
@@ -42832,7 +42856,11 @@
           <t>Additions to intangible assets 14</t>
         </is>
       </c>
-      <c r="D329" t="inlineStr"/>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E329" t="inlineStr">
         <is>
           <t>-</t>
@@ -45340,7 +45368,11 @@
           <t>Depreciation – property, plant and equipment 13</t>
         </is>
       </c>
-      <c r="D353" t="inlineStr"/>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E353" t="inlineStr">
         <is>
           <t>-</t>
@@ -45444,7 +45476,11 @@
           <t>Amortization – intangible assets 14</t>
         </is>
       </c>
-      <c r="D354" t="inlineStr"/>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E354" t="inlineStr">
         <is>
           <t>-</t>
@@ -48586,7 +48622,11 @@
           <t>Depreciation – property, plant and equipment</t>
         </is>
       </c>
-      <c r="D384" t="inlineStr"/>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E384" t="inlineStr">
         <is>
           <t>-</t>
@@ -48686,7 +48726,11 @@
           <t>Amortization – intangible assets</t>
         </is>
       </c>
-      <c r="D385" t="inlineStr"/>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E385" t="inlineStr">
         <is>
           <t>-</t>
@@ -55434,7 +55478,11 @@
           <t>Proceeds on disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D449" t="inlineStr"/>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E449" t="inlineStr">
         <is>
           <t>-</t>
@@ -56800,7 +56848,11 @@
           <t>Depreciation – property, plant and equipment</t>
         </is>
       </c>
-      <c r="D462" t="inlineStr"/>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E462" t="inlineStr">
         <is>
           <t>-</t>
@@ -56898,7 +56950,11 @@
           <t>Amortization – intangible assets</t>
         </is>
       </c>
-      <c r="D463" t="inlineStr"/>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E463" s="5" t="n">
         <v>1.697228</v>
       </c>
@@ -58048,7 +58104,11 @@
           <t>Proceeds on disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D474" t="inlineStr"/>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E474" t="inlineStr">
         <is>
           <t>-</t>
@@ -59526,7 +59586,11 @@
           <t>Proceeds on disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D488" t="inlineStr"/>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E488" t="inlineStr">
         <is>
           <t>-</t>
@@ -62136,7 +62200,11 @@
           <t>Additions to intangible assets</t>
         </is>
       </c>
-      <c r="D513" t="inlineStr"/>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E513" t="inlineStr">
         <is>
           <t>-</t>
@@ -67690,7 +67758,11 @@
           <t>Amortization – intangible assets 12</t>
         </is>
       </c>
-      <c r="D566" t="inlineStr"/>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E566" t="inlineStr">
         <is>
           <t>-</t>
@@ -70328,7 +70400,11 @@
           <t>Amortization – intangible assets 13</t>
         </is>
       </c>
-      <c r="D592" t="inlineStr"/>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E592" t="inlineStr">
         <is>
           <t>-</t>
@@ -74186,7 +74262,11 @@
           <t>Amortization – intangible assets 14</t>
         </is>
       </c>
-      <c r="D629" t="inlineStr"/>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E629" t="inlineStr">
         <is>
           <t>-</t>
@@ -77934,7 +78014,11 @@
           <t>Depreciation – property, plant and equipment 13</t>
         </is>
       </c>
-      <c r="D665" t="inlineStr"/>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E665" t="inlineStr">
         <is>
           <t>-</t>
@@ -80018,7 +80102,11 @@
           <t>Depreciation – property, plant and equipment 11</t>
         </is>
       </c>
-      <c r="D685" t="inlineStr"/>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E685" t="inlineStr">
         <is>
           <t>-</t>
@@ -81674,7 +81762,11 @@
           <t>Depreciation – property, plant and equipment 11</t>
         </is>
       </c>
-      <c r="D701" t="inlineStr"/>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E701" t="inlineStr">
         <is>
           <t>-</t>
@@ -81778,7 +81870,11 @@
           <t>Amortization – intangible assets 12</t>
         </is>
       </c>
-      <c r="D702" t="inlineStr"/>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E702" t="inlineStr">
         <is>
           <t>-</t>
@@ -84096,7 +84192,11 @@
           <t>Depreciation – property, plant and equipment 12</t>
         </is>
       </c>
-      <c r="D724" t="inlineStr"/>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E724" t="inlineStr">
         <is>
           <t>-</t>
@@ -84200,7 +84300,11 @@
           <t>Amortization – intangible assets 13</t>
         </is>
       </c>
-      <c r="D725" t="inlineStr"/>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E725" t="inlineStr">
         <is>
           <t>-</t>
@@ -85564,7 +85668,11 @@
           <t>Depreciation – property, plant and equipment</t>
         </is>
       </c>
-      <c r="D738" t="inlineStr"/>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E738" t="inlineStr">
         <is>
           <t>-</t>
@@ -85664,7 +85772,11 @@
           <t>Amortization – intangible assets</t>
         </is>
       </c>
-      <c r="D739" t="inlineStr"/>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E739" s="5" t="n">
         <v>1.697228</v>
       </c>

--- a/output/pdf_financials_xlsx/MTY.xlsx
+++ b/output/pdf_financials_xlsx/MTY.xlsx
@@ -12186,7 +12186,11 @@
           <t>Lease liabilities 10</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>
@@ -15056,7 +15060,11 @@
           <t>Lease liabilities 11</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>-</t>
@@ -17534,7 +17542,11 @@
           <t>Lease liabilities 12</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>-</t>
@@ -43588,7 +43600,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D336" t="inlineStr"/>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E336" t="inlineStr">
         <is>
           <t>-</t>
@@ -63974,7 +63990,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D530" t="inlineStr"/>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E530" s="5" t="n">
         <v>-0.057531</v>
       </c>
